--- a/34th_Backgammon-championships_5c_output.xlsx
+++ b/34th_Backgammon-championships_5c_output.xlsx
@@ -1015,7 +1015,7 @@
         <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>8</v>
@@ -1091,7 +1091,7 @@
         <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>3</v>
@@ -1140,7 +1140,7 @@
         <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
         <v>4</v>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
@@ -1174,7 +1174,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -1220,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1446,7 +1446,7 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
